--- a/data/dividends_info_20260511.xlsx
+++ b/data/dividends_info_20260511.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>49.98500061035156</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1800540140062769</v>
+        <v>0.178926444065806</v>
       </c>
       <c r="J2" t="n">
         <v>308</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57.65000152587891</v>
+        <v>57.70000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.214223731955622</v>
+        <v>1.213171561081864</v>
       </c>
       <c r="J3" t="n">
         <v>287</v>
@@ -616,8 +616,12 @@
           <t>IT0005337818</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.631578947368421</v>
+      </c>
       <c r="J4" t="n">
         <v>217</v>
       </c>
@@ -707,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>49.98500061035156</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1800540140062769</v>
+        <v>0.178926444065806</v>
       </c>
       <c r="J6" t="n">
         <v>217</v>
@@ -754,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.065000057220459</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I7" t="n">
-        <v>3.728813455997861</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J7" t="n">
         <v>196</v>
@@ -801,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.04000091552734</v>
+        <v>23.45999908447266</v>
       </c>
       <c r="I8" t="n">
-        <v>1.171874953433873</v>
+        <v>1.150895185578688</v>
       </c>
       <c r="J8" t="n">
         <v>196</v>
@@ -848,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.860000133514404</v>
+        <v>5.769999980926514</v>
       </c>
       <c r="I9" t="n">
-        <v>3.412969205515265</v>
+        <v>3.466204517523849</v>
       </c>
       <c r="J9" t="n">
         <v>189</v>
@@ -895,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6.400000095367432</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9374999860301615</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J10" t="n">
         <v>161</v>
@@ -1036,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J13" t="n">
         <v>140</v>
@@ -1083,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.04000091552734</v>
+        <v>23.45999908447266</v>
       </c>
       <c r="I14" t="n">
-        <v>1.171874953433873</v>
+        <v>1.150895185578688</v>
       </c>
       <c r="J14" t="n">
         <v>133</v>
@@ -1130,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>49.98500061035156</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1800540140062769</v>
+        <v>0.178926444065806</v>
       </c>
       <c r="J15" t="n">
         <v>133</v>
@@ -1224,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>4.980000019073486</v>
+        <v>4.96999979019165</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7630522059128382</v>
+        <v>0.7645875574279384</v>
       </c>
       <c r="J17" t="n">
         <v>84</v>
@@ -1271,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.909999847412109</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="I18" t="n">
-        <v>4.230118552532127</v>
+        <v>4.222972918549448</v>
       </c>
       <c r="J18" t="n">
         <v>77</v>
@@ -1318,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>9.704999923706055</v>
+        <v>9.883000373840332</v>
       </c>
       <c r="I19" t="n">
-        <v>2.679031448160111</v>
+        <v>2.630780027978177</v>
       </c>
       <c r="J19" t="n">
         <v>70</v>
@@ -1365,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>15.19999980926514</v>
+        <v>15.22000026702881</v>
       </c>
       <c r="I20" t="n">
-        <v>3.947368470585578</v>
+        <v>3.942181271177663</v>
       </c>
       <c r="J20" t="n">
         <v>70</v>
@@ -1412,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>3.703999996185303</v>
+        <v>3.71399998664856</v>
       </c>
       <c r="I21" t="n">
-        <v>5.939524844129992</v>
+        <v>5.923532600723665</v>
       </c>
       <c r="J21" t="n">
         <v>70</v>
@@ -1506,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6.204999923706055</v>
+        <v>6.21999979019165</v>
       </c>
       <c r="I23" t="n">
-        <v>1.611603565343367</v>
+        <v>1.607717096030944</v>
       </c>
       <c r="J23" t="n">
         <v>70</v>
@@ -1600,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5.349999904632568</v>
+        <v>5.329999923706055</v>
       </c>
       <c r="I25" t="n">
-        <v>2.24299069418846</v>
+        <v>2.251407161682689</v>
       </c>
       <c r="J25" t="n">
         <v>63</v>
@@ -1694,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2.160000085830688</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I27" t="n">
-        <v>3.935185028814982</v>
+        <v>3.794642840987262</v>
       </c>
       <c r="J27" t="n">
         <v>56</v>
@@ -1741,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.170000076293945</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I28" t="n">
-        <v>1.678657043627969</v>
+        <v>1.643192399977255</v>
       </c>
       <c r="J28" t="n">
         <v>56</v>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>37.40000152587891</v>
+        <v>36.5</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4010695023533825</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="J29" t="n">
         <v>56</v>
@@ -1835,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>5.849999904632568</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6837606949074361</v>
+        <v>0.6896551497342619</v>
       </c>
       <c r="J30" t="n">
         <v>49</v>
@@ -1882,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>23.28000068664551</v>
+        <v>23.47999954223633</v>
       </c>
       <c r="I31" t="n">
-        <v>1.073883129837757</v>
+        <v>1.064735966243503</v>
       </c>
       <c r="J31" t="n">
         <v>42</v>
@@ -1929,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6964285714285714</v>
+        <v>0.7090909090909091</v>
       </c>
       <c r="J32" t="n">
         <v>42</v>
@@ -1976,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1.934999942779541</v>
+        <v>1.855000019073486</v>
       </c>
       <c r="I33" t="n">
-        <v>1.705426407020818</v>
+        <v>1.778975722948103</v>
       </c>
       <c r="J33" t="n">
         <v>42</v>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>5.139999866485596</v>
+        <v>5.125</v>
       </c>
       <c r="I34" t="n">
-        <v>5.642023492858249</v>
+        <v>5.658536585365853</v>
       </c>
       <c r="J34" t="n">
         <v>42</v>
@@ -2070,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.881999969482422</v>
+        <v>3.895999908447266</v>
       </c>
       <c r="I35" t="n">
-        <v>4.121586843323248</v>
+        <v>4.106776277203952</v>
       </c>
       <c r="J35" t="n">
         <v>42</v>
@@ -2117,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2.565999984741211</v>
+        <v>2.634000062942505</v>
       </c>
       <c r="I36" t="n">
-        <v>5.401402993927852</v>
+        <v>5.261958871981446</v>
       </c>
       <c r="J36" t="n">
         <v>42</v>
@@ -2164,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>51.08000183105469</v>
+        <v>51.31000137329102</v>
       </c>
       <c r="I37" t="n">
-        <v>1.233359391966553</v>
+        <v>1.227830799334067</v>
       </c>
       <c r="J37" t="n">
         <v>42</v>
@@ -2211,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5.409999847412109</v>
+        <v>5.295000076293945</v>
       </c>
       <c r="I38" t="n">
-        <v>2.587800442674124</v>
+        <v>2.644003739051657</v>
       </c>
       <c r="J38" t="n">
         <v>42</v>
@@ -2258,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>19.20000076293945</v>
+        <v>19.14999961853027</v>
       </c>
       <c r="I39" t="n">
-        <v>4.06249983857076</v>
+        <v>4.073107130745016</v>
       </c>
       <c r="J39" t="n">
         <v>42</v>
@@ -2305,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>23.88999938964844</v>
+        <v>24.22999954223633</v>
       </c>
       <c r="I40" t="n">
-        <v>3.5579741386193</v>
+        <v>3.508047940811263</v>
       </c>
       <c r="J40" t="n">
         <v>42</v>
@@ -2352,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>49.98500061035156</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1800540140062769</v>
+        <v>0.178926444065806</v>
       </c>
       <c r="J41" t="n">
         <v>42</v>
@@ -2399,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.399999976158142</v>
+        <v>1.350000023841858</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7142857264499277</v>
+        <v>0.7407407276587887</v>
       </c>
       <c r="J42" t="n">
         <v>42</v>
@@ -2446,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>6.407999992370605</v>
+        <v>6.464000225067139</v>
       </c>
       <c r="I43" t="n">
-        <v>2.829275908487151</v>
+        <v>2.804764753827293</v>
       </c>
       <c r="J43" t="n">
         <v>42</v>
@@ -2493,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>8.770000457763672</v>
+        <v>8.689999580383301</v>
       </c>
       <c r="I44" t="n">
-        <v>2.964652068744582</v>
+        <v>2.991944908569625</v>
       </c>
       <c r="J44" t="n">
         <v>42</v>
@@ -2540,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>9.961999893188477</v>
+        <v>10.02499961853027</v>
       </c>
       <c r="I45" t="n">
-        <v>2.780566181188166</v>
+        <v>2.763092374467441</v>
       </c>
       <c r="J45" t="n">
         <v>42</v>
@@ -2587,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1.169999957084656</v>
+        <v>1.184999942779541</v>
       </c>
       <c r="I46" t="n">
-        <v>1.15384619616898</v>
+        <v>1.139240561339973</v>
       </c>
       <c r="J46" t="n">
         <v>35</v>
@@ -2634,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>3.690000057220459</v>
+        <v>3.70199990272522</v>
       </c>
       <c r="I47" t="n">
-        <v>2.981029764071574</v>
+        <v>2.971366906817683</v>
       </c>
       <c r="J47" t="n">
         <v>35</v>
@@ -2728,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>3.174999952316284</v>
+        <v>3.184999942779541</v>
       </c>
       <c r="I49" t="n">
-        <v>5.039370154423904</v>
+        <v>5.023547970941827</v>
       </c>
       <c r="J49" t="n">
         <v>28</v>
@@ -2822,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>27.35000038146973</v>
+        <v>27.5</v>
       </c>
       <c r="I51" t="n">
-        <v>4.058500857470011</v>
+        <v>4.036363636363636</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
@@ -2869,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>0.9100000262260437</v>
+        <v>0.8999999761581421</v>
       </c>
       <c r="I52" t="n">
-        <v>3.296703201692877</v>
+        <v>3.333333421636513</v>
       </c>
       <c r="J52" t="n">
         <v>21</v>
@@ -2916,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>0.5099999904632568</v>
+        <v>0.5040000081062317</v>
       </c>
       <c r="I53" t="n">
-        <v>4.509804005899691</v>
+        <v>4.563491990093802</v>
       </c>
       <c r="J53" t="n">
         <v>21</v>
@@ -2963,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>19.89999961853027</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="I54" t="n">
-        <v>3.015075434681407</v>
+        <v>3.030303147067567</v>
       </c>
       <c r="J54" t="n">
         <v>21</v>
@@ -3010,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>8.899999618530273</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I55" t="n">
-        <v>2.247191107554537</v>
+        <v>2.207505416522502</v>
       </c>
       <c r="J55" t="n">
         <v>21</v>
@@ -3057,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>2.539999961853027</v>
+        <v>2.515000104904175</v>
       </c>
       <c r="I56" t="n">
-        <v>7.086614279658614</v>
+        <v>7.157057355544653</v>
       </c>
       <c r="J56" t="n">
         <v>14</v>
@@ -3151,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>13.78999996185303</v>
+        <v>13.71000003814697</v>
       </c>
       <c r="I58" t="n">
-        <v>1.81290790929347</v>
+        <v>1.823486501126149</v>
       </c>
       <c r="J58" t="n">
         <v>14</v>
@@ -3198,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>3.369999885559082</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8902077453638549</v>
+        <v>0.8771929628875695</v>
       </c>
       <c r="J59" t="n">
         <v>14</v>
@@ -3245,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>3.740000009536743</v>
+        <v>3.819999933242798</v>
       </c>
       <c r="I60" t="n">
-        <v>4.010695176938778</v>
+        <v>3.926701639302517</v>
       </c>
       <c r="J60" t="n">
         <v>14</v>
@@ -3292,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>14.19999980926514</v>
+        <v>14</v>
       </c>
       <c r="I61" t="n">
-        <v>4.084507097116753</v>
+        <v>4.142857142857142</v>
       </c>
       <c r="J61" t="n">
         <v>14</v>
@@ -3339,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>2.335000038146973</v>
+        <v>2.342000007629395</v>
       </c>
       <c r="I62" t="n">
-        <v>4.453961383338268</v>
+        <v>4.440649003467351</v>
       </c>
       <c r="J62" t="n">
         <v>7</v>
@@ -3386,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>10.89999961853027</v>
+        <v>10.76000022888184</v>
       </c>
       <c r="I63" t="n">
-        <v>2.660550551827476</v>
+        <v>2.695167228914979</v>
       </c>
       <c r="J63" t="n">
         <v>7</v>
@@ -3433,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>2.065000057220459</v>
+        <v>2.049999952316284</v>
       </c>
       <c r="I64" t="n">
-        <v>3.728813455997861</v>
+        <v>3.756097648343753</v>
       </c>
       <c r="J64" t="n">
         <v>7</v>
@@ -3480,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>39.20999908447266</v>
+        <v>39.41999816894531</v>
       </c>
       <c r="I65" t="n">
-        <v>4.182606575600374</v>
+        <v>4.16032490151655</v>
       </c>
       <c r="J65" t="n">
         <v>7</v>
@@ -3527,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>35.97000122070312</v>
+        <v>35.72999954223633</v>
       </c>
       <c r="I66" t="n">
-        <v>5.560188857733114</v>
+        <v>5.597537155397402</v>
       </c>
       <c r="J66" t="n">
         <v>7</v>
@@ -3574,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>3.788000106811523</v>
+        <v>3.789999961853027</v>
       </c>
       <c r="I67" t="n">
-        <v>2.639915448264681</v>
+        <v>2.638522453997795</v>
       </c>
       <c r="J67" t="n">
         <v>7</v>
@@ -3621,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>28.85000038146973</v>
+        <v>29.5</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5145927141663245</v>
+        <v>0.5032542372881356</v>
       </c>
       <c r="J68" t="n">
         <v>7</v>
@@ -3668,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>22.18000030517578</v>
+        <v>21.02000045776367</v>
       </c>
       <c r="I69" t="n">
-        <v>4.147880916779405</v>
+        <v>4.376783919908055</v>
       </c>
       <c r="J69" t="n">
         <v>7</v>
@@ -3715,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>10.60000038146973</v>
+        <v>10.40999984741211</v>
       </c>
       <c r="I70" t="n">
-        <v>2.830188577393277</v>
+        <v>2.881844422645011</v>
       </c>
       <c r="J70" t="n">
         <v>7</v>
@@ -3762,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>82.87999725341797</v>
+        <v>82.30000305175781</v>
       </c>
       <c r="I71" t="n">
-        <v>1.254826296410272</v>
+        <v>1.263669454964603</v>
       </c>
       <c r="J71" t="n">
         <v>7</v>
@@ -3809,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>47.93000030517578</v>
+        <v>47.61000061035156</v>
       </c>
       <c r="I72" t="n">
-        <v>1.460463166165283</v>
+        <v>1.47027933422837</v>
       </c>
       <c r="J72" t="n">
         <v>7</v>
@@ -3856,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>57.65000152587891</v>
+        <v>57.70000076293945</v>
       </c>
       <c r="I73" t="n">
-        <v>3.816131729003384</v>
+        <v>3.812824906257287</v>
       </c>
       <c r="J73" t="n">
         <v>7</v>
@@ -3903,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>9.36299991607666</v>
+        <v>9.329999923706055</v>
       </c>
       <c r="I74" t="n">
-        <v>9.185090331180547</v>
+        <v>9.217577781698324</v>
       </c>
       <c r="J74" t="n">
         <v>7</v>
@@ -3950,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>12.69400024414062</v>
+        <v>12.58199977874756</v>
       </c>
       <c r="I75" t="n">
-        <v>4.411532922874239</v>
+        <v>4.450802812331187</v>
       </c>
       <c r="J75" t="n">
         <v>7</v>
@@ -3997,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>2.240000009536743</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I76" t="n">
-        <v>1.785714278111652</v>
+        <v>1.80995471988946</v>
       </c>
       <c r="J76" t="n">
         <v>7</v>
@@ -4044,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>9.550000190734863</v>
+        <v>9.350000381469727</v>
       </c>
       <c r="I77" t="n">
-        <v>3.141361193804492</v>
+        <v>3.20855601882706</v>
       </c>
       <c r="J77" t="n">
         <v>7</v>
@@ -4091,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>2.230000019073486</v>
+        <v>2.25</v>
       </c>
       <c r="I78" t="n">
-        <v>4.843049285931015</v>
+        <v>4.8</v>
       </c>
       <c r="J78" t="n">
         <v>7</v>
@@ -4138,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>85.80000305175781</v>
+        <v>84.09999847412109</v>
       </c>
       <c r="I79" t="n">
-        <v>2.400932315535385</v>
+        <v>2.449464967153233</v>
       </c>
       <c r="J79" t="n">
         <v>7</v>
@@ -4185,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>15.92000007629395</v>
+        <v>15.75</v>
       </c>
       <c r="I80" t="n">
-        <v>4.711055253804963</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="J80" t="n">
         <v>7</v>
@@ -4232,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>14.52999973297119</v>
+        <v>14.55000019073486</v>
       </c>
       <c r="I81" t="n">
-        <v>2.064693775040104</v>
+        <v>2.061855643074381</v>
       </c>
       <c r="J81" t="n">
         <v>7</v>
@@ -4326,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>34.93999862670898</v>
+        <v>34.09999847412109</v>
       </c>
       <c r="I83" t="n">
-        <v>2.432741938776836</v>
+        <v>2.492668733240781</v>
       </c>
       <c r="J83" t="n">
         <v>7</v>
@@ -4373,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>69.01999664306641</v>
+        <v>66.69999694824219</v>
       </c>
       <c r="I84" t="n">
-        <v>1.883512117108448</v>
+        <v>1.949025576431095</v>
       </c>
       <c r="J84" t="n">
         <v>7</v>
@@ -4420,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>8.039999961853027</v>
+        <v>8.060000419616699</v>
       </c>
       <c r="I85" t="n">
-        <v>7.462686602572003</v>
+        <v>7.444168346935813</v>
       </c>
       <c r="J85" t="n">
         <v>7</v>
@@ -4467,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>6.150000095367432</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I86" t="n">
-        <v>7.642276304256217</v>
+        <v>7.460317234453558</v>
       </c>
       <c r="J86" t="n">
         <v>7</v>
@@ -4514,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>5.860000133514404</v>
+        <v>5.769999980926514</v>
       </c>
       <c r="I87" t="n">
-        <v>3.412969205515265</v>
+        <v>3.466204517523849</v>
       </c>
       <c r="J87" t="n">
         <v>7</v>
@@ -4561,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>23.21999931335449</v>
+        <v>23.31999969482422</v>
       </c>
       <c r="I88" t="n">
-        <v>4.30663234096166</v>
+        <v>4.288164721639967</v>
       </c>
       <c r="J88" t="n">
         <v>7</v>
@@ -4655,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>23.04000091552734</v>
+        <v>23.45999908447266</v>
       </c>
       <c r="I90" t="n">
-        <v>1.171874953433873</v>
+        <v>1.150895185578688</v>
       </c>
       <c r="J90" t="n">
         <v>7</v>
@@ -4702,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>8.220000267028809</v>
+        <v>8.140000343322754</v>
       </c>
       <c r="I91" t="n">
-        <v>2.433089945291349</v>
+        <v>2.457002353372873</v>
       </c>
       <c r="J91" t="n">
         <v>7</v>
@@ -4749,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>9.020000457763672</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I92" t="n">
-        <v>2.660753745233214</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J92" t="n">
         <v>7</v>
@@ -4796,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>21.81999969482422</v>
+        <v>21.92000007629395</v>
       </c>
       <c r="I93" t="n">
-        <v>3.620531673001769</v>
+        <v>3.604014585996146</v>
       </c>
       <c r="J93" t="n">
         <v>7</v>
@@ -4843,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>5.159999847412109</v>
+        <v>5.179999828338623</v>
       </c>
       <c r="I94" t="n">
-        <v>1.802325634692455</v>
+        <v>1.795366854863928</v>
       </c>
       <c r="J94" t="n">
         <v>7</v>
@@ -4890,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>6.400000095367432</v>
+        <v>6.550000190734863</v>
       </c>
       <c r="I95" t="n">
-        <v>0.9374999860301615</v>
+        <v>0.9160305076764956</v>
       </c>
       <c r="J95" t="n">
         <v>7</v>
@@ -4937,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>35.93999862670898</v>
+        <v>36.13999938964844</v>
       </c>
       <c r="I96" t="n">
-        <v>0.9738453349296896</v>
+        <v>0.9684560207830283</v>
       </c>
       <c r="J96" t="n">
         <v>7</v>
@@ -4984,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>7.184999942779541</v>
+        <v>7.375</v>
       </c>
       <c r="I97" t="n">
-        <v>7.714683429566838</v>
+        <v>7.515932203389831</v>
       </c>
       <c r="J97" t="n">
         <v>7</v>
@@ -5078,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>12.85000038146973</v>
+        <v>13</v>
       </c>
       <c r="I99" t="n">
-        <v>1.556420187258585</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="J99" t="n">
         <v>7</v>
@@ -5125,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>7.139999866485596</v>
+        <v>7</v>
       </c>
       <c r="I100" t="n">
-        <v>1.442577057787789</v>
+        <v>1.471428571428571</v>
       </c>
       <c r="J100" t="n">
         <v>7</v>
@@ -5172,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5.854000091552734</v>
+        <v>5.857999801635742</v>
       </c>
       <c r="I101" t="n">
-        <v>3.245643953340011</v>
+        <v>3.243427900884289</v>
       </c>
       <c r="J101" t="n">
         <v>7</v>
@@ -5219,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>10.32999992370605</v>
+        <v>10.41499996185303</v>
       </c>
       <c r="I102" t="n">
-        <v>4.181994222561553</v>
+        <v>4.14786367337767</v>
       </c>
       <c r="J102" t="n">
         <v>7</v>
@@ -5266,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>26.38999938964844</v>
+        <v>26.29999923706055</v>
       </c>
       <c r="I103" t="n">
-        <v>1.667298257583861</v>
+        <v>1.673003850813713</v>
       </c>
       <c r="J103" t="n">
         <v>7</v>
@@ -5360,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>8.430000305175781</v>
+        <v>8.380000114440918</v>
       </c>
       <c r="I105" t="n">
-        <v>5.57532601406234</v>
+        <v>5.608591808848162</v>
       </c>
       <c r="J105" t="n">
         <v>7</v>
@@ -5407,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>52.72000122070312</v>
+        <v>51.77999877929688</v>
       </c>
       <c r="I106" t="n">
-        <v>2.65553863350485</v>
+        <v>2.703746684057011</v>
       </c>
       <c r="J106" t="n">
         <v>7</v>
@@ -5454,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4.26200008392334</v>
+        <v>4.107999801635742</v>
       </c>
       <c r="I107" t="n">
-        <v>7.03894871170059</v>
+        <v>7.302824111153672</v>
       </c>
       <c r="J107" t="n">
         <v>7</v>
@@ -5548,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>3.509999990463257</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="I109" t="n">
-        <v>4.843304856464204</v>
+        <v>4.98533711791938</v>
       </c>
       <c r="J109" t="n">
         <v>7</v>
@@ -5595,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>21.35000038146973</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="I110" t="n">
-        <v>3.278688466008412</v>
+        <v>3.39805818950212</v>
       </c>
       <c r="J110" t="n">
         <v>7</v>
@@ -5642,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>2.420000076293945</v>
+        <v>2.359999895095825</v>
       </c>
       <c r="I111" t="n">
-        <v>1.446280946139471</v>
+        <v>1.483050913380607</v>
       </c>
       <c r="J111" t="n">
         <v>7</v>
@@ -5689,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>5.920000076293945</v>
+        <v>5.809999942779541</v>
       </c>
       <c r="I112" t="n">
-        <v>5.574324252485273</v>
+        <v>5.679862362307114</v>
       </c>
       <c r="J112" t="n">
         <v>7</v>
@@ -5736,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>0.9739999771118164</v>
+        <v>0.9800000190734863</v>
       </c>
       <c r="I113" t="n">
-        <v>7.186858485106917</v>
+        <v>7.142857003837566</v>
       </c>
       <c r="J113" t="n">
         <v>7</v>
@@ -5783,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>50.5</v>
+        <v>49.91999816894531</v>
       </c>
       <c r="I114" t="n">
-        <v>1.405940594059406</v>
+        <v>1.422275693194403</v>
       </c>
       <c r="J114" t="n">
         <v>7</v>
@@ -5830,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>97.59999847412109</v>
+        <v>95.84999847412109</v>
       </c>
       <c r="I115" t="n">
-        <v>1.383196742936381</v>
+        <v>1.408450726647108</v>
       </c>
       <c r="J115" t="n">
         <v>7</v>
@@ -5877,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>7.099999904632568</v>
+        <v>7.139999866485596</v>
       </c>
       <c r="I116" t="n">
-        <v>1.126760578514967</v>
+        <v>1.120448200223526</v>
       </c>
       <c r="J116" t="n">
         <v>7</v>
@@ -5971,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>4.39799976348877</v>
+        <v>4.434999942779541</v>
       </c>
       <c r="I118" t="n">
-        <v>3.86539356848772</v>
+        <v>3.833145483502671</v>
       </c>
       <c r="J118" t="n">
         <v>7</v>
@@ -6065,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>56.5</v>
+        <v>58.09999847412109</v>
       </c>
       <c r="I120" t="n">
-        <v>0.7964601769911505</v>
+        <v>0.7745266984825121</v>
       </c>
       <c r="J120" t="n">
         <v>7</v>
@@ -6112,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>5.139999866485596</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I121" t="n">
-        <v>0.7782101369459655</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J121" t="n">
         <v>7</v>
@@ -6159,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>35.93999862670898</v>
+        <v>36</v>
       </c>
       <c r="I122" t="n">
-        <v>2.921536004789069</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="J122" t="n">
         <v>7</v>
@@ -6253,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>21.26000022888184</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="I124" t="n">
-        <v>1.787394148207806</v>
+        <v>1.802656553013842</v>
       </c>
       <c r="J124" t="n">
         <v>7</v>
@@ -6300,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>25.57999992370605</v>
+        <v>25.92000007629395</v>
       </c>
       <c r="I125" t="n">
-        <v>2.345582493313282</v>
+        <v>2.314814808001298</v>
       </c>
       <c r="J125" t="n">
         <v>7</v>
@@ -6347,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>33.95000076293945</v>
+        <v>33.34999847412109</v>
       </c>
       <c r="I126" t="n">
-        <v>1.030927811884079</v>
+        <v>1.049475310385974</v>
       </c>
       <c r="J126" t="n">
         <v>7</v>
@@ -6394,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>3.619999885559082</v>
+        <v>3.660000085830688</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4696132745146338</v>
+        <v>0.4644808634243957</v>
       </c>
       <c r="J127" t="n">
         <v>7</v>
@@ -6441,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.805000066757202</v>
+        <v>2.789999961853027</v>
       </c>
       <c r="I128" t="n">
-        <v>0.3565062303745603</v>
+        <v>0.3584229439687277</v>
       </c>
       <c r="J128" t="n">
         <v>7</v>
@@ -6488,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>22.45000076293945</v>
+        <v>22.54000091552734</v>
       </c>
       <c r="I129" t="n">
-        <v>4.988863972997723</v>
+        <v>4.968943897550844</v>
       </c>
       <c r="J129" t="n">
         <v>7</v>
@@ -6535,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1.610000014305115</v>
+        <v>1.590000033378601</v>
       </c>
       <c r="I130" t="n">
-        <v>6.211180069036247</v>
+        <v>6.289308044070249</v>
       </c>
       <c r="J130" t="n">
         <v>7</v>
@@ -6582,10 +6586,10 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>8.760000228881836</v>
+        <v>8.859999656677246</v>
       </c>
       <c r="I131" t="n">
-        <v>2.968036452131321</v>
+        <v>2.93453735976224</v>
       </c>
       <c r="J131" t="n">
         <v>7</v>
@@ -6629,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.111999988555908</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I132" t="n">
-        <v>4.370265175195888</v>
+        <v>4.395238294839327</v>
       </c>
       <c r="J132" t="n">
         <v>7</v>
@@ -6676,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.039999961853027</v>
+        <v>9</v>
       </c>
       <c r="I133" t="n">
-        <v>3.871681432266917</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6770,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>6</v>
+        <v>6.099999904632568</v>
       </c>
       <c r="I135" t="n">
-        <v>5</v>
+        <v>4.918032863773797</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -6859,8 +6863,12 @@
           <t>IT0005337818</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr"/>
-      <c r="I137" t="inlineStr"/>
+      <c r="H137" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.631578947368421</v>
+      </c>
       <c r="J137" t="n">
         <v>0</v>
       </c>
@@ -6903,10 +6911,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>19.8799991607666</v>
+        <v>19.65999984741211</v>
       </c>
       <c r="I138" t="n">
-        <v>2.515090649434008</v>
+        <v>2.543235014652435</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -6950,10 +6958,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>2.220000028610229</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I139" t="n">
-        <v>2.702702667871647</v>
+        <v>2.727272668160684</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -6997,10 +7005,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>15.97999954223633</v>
+        <v>15.76000022888184</v>
       </c>
       <c r="I140" t="n">
-        <v>3.128911228554561</v>
+        <v>3.172588786411933</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -7043,8 +7051,12 @@
           <t>IT0005430951</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+      <c r="H141" t="n">
+        <v>4.099999904632568</v>
+      </c>
+      <c r="I141" t="n">
+        <v>2.439024446976463</v>
+      </c>
       <c r="J141" t="n">
         <v>0</v>
       </c>
@@ -7087,10 +7099,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>3.569999933242798</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I142" t="n">
-        <v>3.081232550614696</v>
+        <v>3.089887690113706</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -7133,8 +7145,12 @@
           <t>IT0005545238</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr"/>
-      <c r="I143" t="inlineStr"/>
+      <c r="H143" t="n">
+        <v>8.800000190734863</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.9659090699735757</v>
+      </c>
       <c r="J143" t="n">
         <v>0</v>
       </c>
@@ -7219,8 +7235,12 @@
           <t>IT0005521551</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
+      <c r="H145" t="n">
+        <v>1.220000028610229</v>
+      </c>
+      <c r="I145" t="n">
+        <v>2.459016335776212</v>
+      </c>
       <c r="J145" t="n">
         <v>0</v>
       </c>
@@ -7400,10 +7420,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>28.04999923706055</v>
+        <v>28</v>
       </c>
       <c r="I149" t="n">
-        <v>2.174688116190922</v>
+        <v>2.178571428571429</v>
       </c>
       <c r="J149" t="n">
         <v>-7</v>
@@ -7494,10 +7514,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>11.05000019073486</v>
+        <v>11.30000019073486</v>
       </c>
       <c r="I151" t="n">
-        <v>6.334841519613111</v>
+        <v>6.194690160925364</v>
       </c>
       <c r="J151" t="n">
         <v>-7</v>
@@ -7541,10 +7561,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>8.649999618530273</v>
+        <v>8.529999732971191</v>
       </c>
       <c r="I152" t="n">
-        <v>5.901734364315953</v>
+        <v>5.984759859097689</v>
       </c>
       <c r="J152" t="n">
         <v>-7</v>
@@ -7588,10 +7608,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>8.345000267028809</v>
+        <v>8.064999580383301</v>
       </c>
       <c r="I153" t="n">
-        <v>3.235470237991161</v>
+        <v>3.347799306235896</v>
       </c>
       <c r="J153" t="n">
         <v>-7</v>
@@ -7635,10 +7655,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>6.320000171661377</v>
+        <v>6.210000038146973</v>
       </c>
       <c r="I154" t="n">
-        <v>5.537974533123998</v>
+        <v>5.636070818840734</v>
       </c>
       <c r="J154" t="n">
         <v>-7</v>
@@ -7682,10 +7702,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>40.59999847412109</v>
+        <v>40</v>
       </c>
       <c r="I155" t="n">
-        <v>2.709359707737804</v>
+        <v>2.75</v>
       </c>
       <c r="J155" t="n">
         <v>-7</v>
@@ -7729,10 +7749,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>17.95000076293945</v>
+        <v>17.89999961853027</v>
       </c>
       <c r="I156" t="n">
-        <v>4.178272802909796</v>
+        <v>4.189944223370775</v>
       </c>
       <c r="J156" t="n">
         <v>-7</v>
@@ -7776,10 +7796,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>11.69999980926514</v>
+        <v>11.35000038146973</v>
       </c>
       <c r="I157" t="n">
-        <v>3.675213735127469</v>
+        <v>3.788546128174832</v>
       </c>
       <c r="J157" t="n">
         <v>-7</v>
@@ -7823,10 +7843,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>4.139999866485596</v>
+        <v>4.105000019073486</v>
       </c>
       <c r="I158" t="n">
-        <v>3.62318852264441</v>
+        <v>3.654080372790243</v>
       </c>
       <c r="J158" t="n">
         <v>-7</v>
@@ -7870,10 +7890,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>11.97999954223633</v>
+        <v>12.11999988555908</v>
       </c>
       <c r="I159" t="n">
-        <v>1.645818092937874</v>
+        <v>1.626806946053901</v>
       </c>
       <c r="J159" t="n">
         <v>-7</v>
@@ -7964,10 +7984,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>59.79999923706055</v>
+        <v>61</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7859531872848611</v>
+        <v>0.7704918032786885</v>
       </c>
       <c r="J161" t="n">
         <v>-7</v>
@@ -8011,10 +8031,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>77.90000152587891</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5404364268226</v>
+        <v>1.550387566334578</v>
       </c>
       <c r="J162" t="n">
         <v>-7</v>
@@ -8058,10 +8078,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>25.39999961853027</v>
+        <v>25.35000038146973</v>
       </c>
       <c r="I163" t="n">
-        <v>1.062992141948792</v>
+        <v>1.065088741368871</v>
       </c>
       <c r="J163" t="n">
         <v>-7</v>
@@ -8105,10 +8125,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>10.44999980926514</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I164" t="n">
-        <v>3.636363702735056</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J164" t="n">
         <v>-7</v>
@@ -8152,10 +8172,10 @@
         </is>
       </c>
       <c r="H165" t="n">
-        <v>30.20000076293945</v>
+        <v>30.39999961853027</v>
       </c>
       <c r="I165" t="n">
-        <v>0.9933774583481174</v>
+        <v>0.9868421176463945</v>
       </c>
       <c r="J165" t="n">
         <v>-7</v>
@@ -8199,10 +8219,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>0.1764000058174133</v>
+        <v>0.1729999929666519</v>
       </c>
       <c r="I166" t="n">
-        <v>3.968253837386776</v>
+        <v>4.046242939067255</v>
       </c>
       <c r="J166" t="n">
         <v>-14</v>
@@ -8246,10 +8266,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>7.21999979019165</v>
+        <v>7.090000152587891</v>
       </c>
       <c r="I167" t="n">
-        <v>2.216066546391865</v>
+        <v>2.256699528301126</v>
       </c>
       <c r="J167" t="n">
         <v>-14</v>
@@ -8340,10 +8360,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>7.46999979019165</v>
+        <v>7.429999828338623</v>
       </c>
       <c r="I169" t="n">
-        <v>3.346720308188737</v>
+        <v>3.364737628209353</v>
       </c>
       <c r="J169" t="n">
         <v>-14</v>
@@ -8481,10 +8501,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>19.59000015258789</v>
+        <v>19.5</v>
       </c>
       <c r="I172" t="n">
-        <v>3.318019371807577</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J172" t="n">
         <v>-21</v>
@@ -8528,10 +8548,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>12.97999954223633</v>
+        <v>12.88500022888184</v>
       </c>
       <c r="I173" t="n">
-        <v>4.160246679846672</v>
+        <v>4.19091959959446</v>
       </c>
       <c r="J173" t="n">
         <v>-21</v>
@@ -8575,10 +8595,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>5.584000110626221</v>
+        <v>5.489999771118164</v>
       </c>
       <c r="I174" t="n">
-        <v>1.790830910080076</v>
+        <v>1.821493700711625</v>
       </c>
       <c r="J174" t="n">
         <v>-21</v>
@@ -8622,10 +8642,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>8.140000343322754</v>
+        <v>8.279999732971191</v>
       </c>
       <c r="I175" t="n">
-        <v>1.965601882698298</v>
+        <v>1.932367212077019</v>
       </c>
       <c r="J175" t="n">
         <v>-21</v>
@@ -8669,10 +8689,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>282.6499938964844</v>
+        <v>281.1000061035156</v>
       </c>
       <c r="I176" t="n">
-        <v>1.278966947837236</v>
+        <v>1.28601918232217</v>
       </c>
       <c r="J176" t="n">
         <v>-21</v>
@@ -8716,10 +8736,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>27.89999961853027</v>
+        <v>28.60000038146973</v>
       </c>
       <c r="I177" t="n">
-        <v>4.874552037974697</v>
+        <v>4.755244691818816</v>
       </c>
       <c r="J177" t="n">
         <v>-21</v>
@@ -8810,10 +8830,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>15.42000007629395</v>
+        <v>15.26000022888184</v>
       </c>
       <c r="I179" t="n">
-        <v>3.79377430029559</v>
+        <v>3.833551711832873</v>
       </c>
       <c r="J179" t="n">
         <v>-21</v>
@@ -8857,10 +8877,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>20.48999977111816</v>
+        <v>20.46999931335449</v>
       </c>
       <c r="I180" t="n">
-        <v>3.074670605355601</v>
+        <v>3.077674749060652</v>
       </c>
       <c r="J180" t="n">
         <v>-21</v>
@@ -8904,10 +8924,10 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>154.6000061035156</v>
+        <v>156.8999938964844</v>
       </c>
       <c r="I181" t="n">
-        <v>0.5821474543780978</v>
+        <v>0.5736137890443641</v>
       </c>
       <c r="J181" t="n">
         <v>-21</v>
@@ -8951,10 +8971,10 @@
         </is>
       </c>
       <c r="H182" t="n">
-        <v>71.11000061035156</v>
+        <v>70.73000335693359</v>
       </c>
       <c r="I182" t="n">
-        <v>2.419912790367071</v>
+        <v>2.432913782452566</v>
       </c>
       <c r="J182" t="n">
         <v>-21</v>
@@ -8998,10 +9018,10 @@
         </is>
       </c>
       <c r="H183" t="n">
-        <v>26.39999961853027</v>
+        <v>26.60000038146973</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5303030379657029</v>
+        <v>0.526315781925807</v>
       </c>
       <c r="J183" t="n">
         <v>-28</v>
@@ -9720,7 +9740,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -9737,7 +9757,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -9754,7 +9774,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -9781,14 +9801,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -9798,14 +9818,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -9822,7 +9842,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -9849,7 +9869,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -9873,7 +9893,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -9890,7 +9910,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -9975,7 +9995,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9985,14 +10005,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -10002,14 +10022,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -10019,14 +10039,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -10043,7 +10063,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10060,7 +10080,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -10070,7 +10090,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10087,14 +10107,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -10111,7 +10131,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -10128,7 +10148,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -10264,7 +10284,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10274,7 +10294,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10291,14 +10311,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10308,14 +10328,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10325,14 +10345,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10349,7 +10369,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10366,7 +10386,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10383,7 +10403,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10393,14 +10413,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10410,14 +10430,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10434,7 +10454,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10444,14 +10464,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10461,14 +10481,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10485,7 +10505,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10495,14 +10515,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10512,14 +10532,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10529,14 +10549,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10553,7 +10573,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10563,14 +10583,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10580,14 +10600,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10604,7 +10624,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10614,14 +10634,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10631,14 +10651,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10655,7 +10675,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10665,14 +10685,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10689,7 +10709,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10706,7 +10726,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10716,14 +10736,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10733,14 +10753,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10750,14 +10770,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10774,7 +10794,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10784,14 +10804,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10808,7 +10828,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10818,14 +10838,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10842,7 +10862,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10859,7 +10879,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10869,14 +10889,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10893,7 +10913,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10910,7 +10930,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10927,7 +10947,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10961,7 +10981,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10978,7 +10998,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10995,7 +11015,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11012,7 +11032,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11022,14 +11042,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11046,7 +11066,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11063,7 +11083,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11080,7 +11100,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11090,14 +11110,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11114,7 +11134,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11131,7 +11151,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11141,14 +11161,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11158,14 +11178,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11182,7 +11202,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11192,14 +11212,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11209,14 +11229,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11233,7 +11253,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11250,7 +11270,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11260,14 +11280,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11277,14 +11297,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11301,7 +11321,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11311,14 +11331,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11335,7 +11355,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11345,14 +11365,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11362,14 +11382,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11386,7 +11406,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11396,14 +11416,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11420,7 +11440,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11430,14 +11450,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11447,14 +11467,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11464,14 +11484,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11481,14 +11501,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11505,7 +11525,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11522,7 +11542,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11539,7 +11559,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11549,14 +11569,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11566,14 +11586,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11583,14 +11603,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11607,7 +11627,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11617,14 +11637,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11641,7 +11661,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11651,14 +11671,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11668,14 +11688,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11685,14 +11705,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11709,7 +11729,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11719,14 +11739,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11736,14 +11756,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11753,14 +11773,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11770,14 +11790,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11794,7 +11814,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11811,7 +11831,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11821,14 +11841,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11838,14 +11858,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11855,14 +11875,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11872,14 +11892,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11889,14 +11909,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11906,14 +11926,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11923,14 +11943,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11940,14 +11960,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11964,7 +11984,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11974,14 +11994,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11991,14 +12011,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12008,14 +12028,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12025,14 +12045,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12042,14 +12062,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12059,14 +12079,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12083,7 +12103,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -12093,14 +12113,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -12110,14 +12130,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12127,14 +12147,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12144,14 +12164,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12161,14 +12181,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12178,14 +12198,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12212,14 +12232,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12253,7 +12273,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12263,14 +12283,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12287,7 +12307,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12304,7 +12324,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12314,14 +12334,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12331,14 +12351,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12348,14 +12368,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12389,7 +12409,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12406,7 +12426,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12416,14 +12436,14 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12508,7 +12528,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12518,14 +12538,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12542,7 +12562,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12552,14 +12572,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12569,14 +12589,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12586,14 +12606,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12603,14 +12623,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12620,14 +12640,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12644,7 +12664,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12654,14 +12674,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12671,14 +12691,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12695,7 +12715,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12705,14 +12725,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12729,7 +12749,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12746,7 +12766,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12756,14 +12776,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12780,7 +12800,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12790,14 +12810,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12807,14 +12827,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12824,14 +12844,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12848,7 +12868,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12865,7 +12885,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12875,14 +12895,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12899,7 +12919,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12909,14 +12929,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12933,7 +12953,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12950,7 +12970,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12967,7 +12987,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12977,14 +12997,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12994,7 +13014,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13018,7 +13038,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -13028,14 +13048,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -13069,7 +13089,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -13079,14 +13099,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -13096,14 +13116,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13113,7 +13133,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13137,7 +13157,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -13154,7 +13174,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13171,7 +13191,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13188,7 +13208,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13205,7 +13225,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13307,7 +13327,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Homizy SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13317,14 +13337,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13341,7 +13361,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Homizy SIIQ S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13351,14 +13371,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13375,7 +13395,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13409,7 +13429,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13434,188 +13454,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0003132476</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>23.04000091552734</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1.171874953433873</v>
-      </c>
-      <c r="I2" t="n">
-        <v>133</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0003132476</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-11-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-11-25</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>23.04000091552734</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1.171874953433873</v>
-      </c>
-      <c r="I3" t="n">
-        <v>196</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Simone S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005573123</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-22 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1.399999976158142</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>0.7142857264499277</v>
-      </c>
-      <c r="I4" t="n">
-        <v>42</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13626,146 +13467,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>EL.EN. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Farmacosmo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KME Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PININFARINA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>